--- a/runs/RELX/2026-10-14/bear/scratch/gs_no_beta/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/gs_no_beta/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2304.084280813279</v>
+        <v>2369.656704973342</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.09853100000000001</v>
+        <v>0.0907478</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09153044827456001</v>
+        <v>0.08474489885056001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11940.19051632107</v>
+        <v>12125.91339987368</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>48278.15388113929</v>
+        <v>53609.65910595361</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>32552.87179075048</v>
+        <v>37176.52319612525</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>44493.06230707155</v>
+        <v>49302.43659599893</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>37496.06230707155</v>
+        <v>42305.43659599893</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>37088.04565871099</v>
+        <v>42011.91445063779</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>21.26907247013931</v>
+        <v>24.09278885392107</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2126.907247013931</v>
+        <v>2409.278885392107</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.232440546</v>
+        <v>-0.1305381143</v>
       </c>
     </row>
   </sheetData>
